--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127199651</v>
+        <v>127211062</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615757</v>
+        <v>616059</v>
       </c>
       <c r="R3" t="n">
-        <v>7312430</v>
+        <v>7312517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127211062</v>
+        <v>127199651</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616059</v>
+        <v>615757</v>
       </c>
       <c r="R4" t="n">
-        <v>7312517</v>
+        <v>7312430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127206480</v>
+        <v>127216040</v>
       </c>
       <c r="B8" t="n">
-        <v>79059</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1278,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616032</v>
+        <v>615850</v>
       </c>
       <c r="R8" t="n">
-        <v>7312582</v>
+        <v>7312339</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127216040</v>
+        <v>127206480</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,34 +1482,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615850</v>
+        <v>616032</v>
       </c>
       <c r="R10" t="n">
-        <v>7312339</v>
+        <v>7312582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127209866</v>
+        <v>127202357</v>
       </c>
       <c r="B11" t="n">
-        <v>91259</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616160</v>
+        <v>615826</v>
       </c>
       <c r="R11" t="n">
-        <v>7312538</v>
+        <v>7312510</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127202357</v>
+        <v>127209866</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>91333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,34 +1676,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615826</v>
+        <v>616160</v>
       </c>
       <c r="R12" t="n">
-        <v>7312510</v>
+        <v>7312538</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127202904</v>
+        <v>127213092</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,39 +1773,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615830</v>
+        <v>615949</v>
       </c>
       <c r="R13" t="n">
-        <v>7312490</v>
+        <v>7312406</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,11 +1833,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i gammal levande gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127213092</v>
+        <v>127202904</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1870,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615949</v>
+        <v>615830</v>
       </c>
       <c r="R14" t="n">
-        <v>7312406</v>
+        <v>7312490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,6 +1935,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i gammal levande gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127202530</v>
+        <v>127215400</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,34 +1977,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615835</v>
+        <v>615915</v>
       </c>
       <c r="R15" t="n">
-        <v>7312494</v>
+        <v>7312380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,48 +2088,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R16" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2177,7 +2177,7 @@
         <v>127199175</v>
       </c>
       <c r="B17" t="n">
-        <v>79059</v>
+        <v>79090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>127215841</v>
       </c>
       <c r="B18" t="n">
-        <v>79059</v>
+        <v>79090</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>127210564</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>127200148</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127205089</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127208158</v>
+        <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>91337</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,34 +2670,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Innervik, Innervik, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616118</v>
+        <v>615847</v>
       </c>
       <c r="R22" t="n">
-        <v>7312594</v>
+        <v>7312503</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127203005</v>
+        <v>127208158</v>
       </c>
       <c r="B23" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,34 +2767,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Innervik, Innervik, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615847</v>
+        <v>616118</v>
       </c>
       <c r="R23" t="n">
-        <v>7312503</v>
+        <v>7312594</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
         <v>127198843</v>
       </c>
       <c r="B24" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127201066</v>
+        <v>127215584</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,39 +2961,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615797</v>
+        <v>615886</v>
       </c>
       <c r="R25" t="n">
-        <v>7312466</v>
+        <v>7312367</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3026,11 +3021,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3057,10 +3047,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127215584</v>
+        <v>127217294</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615886</v>
+        <v>615776</v>
       </c>
       <c r="R26" t="n">
-        <v>7312367</v>
+        <v>7312289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3154,10 +3144,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127217294</v>
+        <v>127201066</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3165,34 +3155,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615776</v>
+        <v>615797</v>
       </c>
       <c r="R27" t="n">
-        <v>7312289</v>
+        <v>7312466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,6 +3220,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127202125</v>
+        <v>127209165</v>
       </c>
       <c r="B29" t="n">
-        <v>75075</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3359,34 +3359,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615815</v>
+        <v>616119</v>
       </c>
       <c r="R29" t="n">
-        <v>7312514</v>
+        <v>7312620</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,6 +3424,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3448,7 +3458,7 @@
         <v>127216622</v>
       </c>
       <c r="B30" t="n">
-        <v>91506</v>
+        <v>91580</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3542,10 +3552,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127209165</v>
+        <v>127202125</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>75135</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3553,39 +3563,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>616119</v>
+        <v>615815</v>
       </c>
       <c r="R31" t="n">
-        <v>7312620</v>
+        <v>7312514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3618,11 +3623,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127201655</v>
+        <v>127199651</v>
       </c>
       <c r="B2" t="n">
-        <v>91337</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615794</v>
+        <v>615757</v>
       </c>
       <c r="R2" t="n">
-        <v>7312501</v>
+        <v>7312430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127211062</v>
+        <v>127201655</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>91343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616059</v>
+        <v>615794</v>
       </c>
       <c r="R3" t="n">
-        <v>7312517</v>
+        <v>7312501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127199651</v>
+        <v>127211062</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615757</v>
+        <v>616059</v>
       </c>
       <c r="R4" t="n">
-        <v>7312430</v>
+        <v>7312517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127216040</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127206480</v>
       </c>
       <c r="B10" t="n">
-        <v>79090</v>
+        <v>79093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127202357</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127209866</v>
       </c>
       <c r="B12" t="n">
-        <v>91333</v>
+        <v>91339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127213092</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>127202530</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>127199175</v>
       </c>
       <c r="B17" t="n">
-        <v>79090</v>
+        <v>79093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>127215841</v>
       </c>
       <c r="B18" t="n">
-        <v>79090</v>
+        <v>79093</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>127210564</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>127200148</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127205089</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>127208158</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>127198843</v>
       </c>
       <c r="B24" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>127215584</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>127217294</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>127216622</v>
       </c>
       <c r="B30" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>127202125</v>
       </c>
       <c r="B31" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127199651</v>
+        <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615757</v>
+        <v>615794</v>
       </c>
       <c r="R2" t="n">
-        <v>7312430</v>
+        <v>7312501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127201655</v>
+        <v>127211062</v>
       </c>
       <c r="B3" t="n">
-        <v>91343</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615794</v>
+        <v>616059</v>
       </c>
       <c r="R3" t="n">
-        <v>7312501</v>
+        <v>7312517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127211062</v>
+        <v>127199651</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616059</v>
+        <v>615757</v>
       </c>
       <c r="R4" t="n">
-        <v>7312517</v>
+        <v>7312430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127207662</v>
+        <v>127206480</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>79093</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,39 +1375,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616073</v>
+        <v>616032</v>
       </c>
       <c r="R9" t="n">
-        <v>7312575</v>
+        <v>7312582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127206480</v>
+        <v>127207662</v>
       </c>
       <c r="B10" t="n">
-        <v>79093</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,34 +1472,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616032</v>
+        <v>616073</v>
       </c>
       <c r="R10" t="n">
-        <v>7312582</v>
+        <v>7312575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1537,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B15" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,48 +1977,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R15" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127202530</v>
+        <v>127215400</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,34 +2074,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615835</v>
+        <v>615915</v>
       </c>
       <c r="R16" t="n">
-        <v>7312494</v>
+        <v>7312380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3348,50 +3348,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127209165</v>
+        <v>127216622</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>91586</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616119</v>
+        <v>615822</v>
       </c>
       <c r="R29" t="n">
-        <v>7312620</v>
+        <v>7312329</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,11 +3419,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3455,45 +3445,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127216622</v>
+        <v>127202125</v>
       </c>
       <c r="B30" t="n">
-        <v>91586</v>
+        <v>75138</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615822</v>
+        <v>615815</v>
       </c>
       <c r="R30" t="n">
-        <v>7312329</v>
+        <v>7312514</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,10 +3542,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127202125</v>
+        <v>127209165</v>
       </c>
       <c r="B31" t="n">
-        <v>75138</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3563,34 +3553,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615815</v>
+        <v>616119</v>
       </c>
       <c r="R31" t="n">
-        <v>7312514</v>
+        <v>7312620</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3623,6 +3618,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127206480</v>
+        <v>127207662</v>
       </c>
       <c r="B9" t="n">
-        <v>79093</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,34 +1375,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616032</v>
+        <v>616073</v>
       </c>
       <c r="R9" t="n">
-        <v>7312582</v>
+        <v>7312575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1440,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127207662</v>
+        <v>127206480</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>79093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,39 +1482,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616073</v>
+        <v>616032</v>
       </c>
       <c r="R10" t="n">
-        <v>7312575</v>
+        <v>7312582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1668,7 @@
         <v>127209866</v>
       </c>
       <c r="B12" t="n">
-        <v>91339</v>
+        <v>91340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3348,45 +3348,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127216622</v>
+        <v>127202125</v>
       </c>
       <c r="B29" t="n">
-        <v>91586</v>
+        <v>75138</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615822</v>
+        <v>615815</v>
       </c>
       <c r="R29" t="n">
-        <v>7312329</v>
+        <v>7312514</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3445,10 +3445,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127202125</v>
+        <v>127209165</v>
       </c>
       <c r="B30" t="n">
-        <v>75138</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3456,34 +3456,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615815</v>
+        <v>616119</v>
       </c>
       <c r="R30" t="n">
-        <v>7312514</v>
+        <v>7312620</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3516,6 +3521,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3542,50 +3552,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127209165</v>
+        <v>127216622</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>91587</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>616119</v>
+        <v>615822</v>
       </c>
       <c r="R31" t="n">
-        <v>7312620</v>
+        <v>7312329</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3618,11 +3623,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127201655</v>
+        <v>127199651</v>
       </c>
       <c r="B2" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615794</v>
+        <v>615757</v>
       </c>
       <c r="R2" t="n">
-        <v>7312501</v>
+        <v>7312430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127211062</v>
+        <v>127201655</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>91344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616059</v>
+        <v>615794</v>
       </c>
       <c r="R3" t="n">
-        <v>7312517</v>
+        <v>7312501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127199651</v>
+        <v>127211062</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615757</v>
+        <v>616059</v>
       </c>
       <c r="R4" t="n">
-        <v>7312430</v>
+        <v>7312517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -3348,10 +3348,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127202125</v>
+        <v>127209165</v>
       </c>
       <c r="B29" t="n">
-        <v>75138</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3359,34 +3359,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615815</v>
+        <v>616119</v>
       </c>
       <c r="R29" t="n">
-        <v>7312514</v>
+        <v>7312620</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,6 +3424,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3445,50 +3455,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127209165</v>
+        <v>127216622</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>91587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>616119</v>
+        <v>615822</v>
       </c>
       <c r="R30" t="n">
-        <v>7312620</v>
+        <v>7312329</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3521,11 +3526,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3552,45 +3552,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127216622</v>
+        <v>127202125</v>
       </c>
       <c r="B31" t="n">
-        <v>91587</v>
+        <v>75138</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615822</v>
+        <v>615815</v>
       </c>
       <c r="R31" t="n">
-        <v>7312329</v>
+        <v>7312514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127199651</v>
+        <v>127211062</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615757</v>
+        <v>616059</v>
       </c>
       <c r="R2" t="n">
-        <v>7312430</v>
+        <v>7312517</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127211062</v>
+        <v>127199651</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616059</v>
+        <v>615757</v>
       </c>
       <c r="R4" t="n">
-        <v>7312517</v>
+        <v>7312430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127216040</v>
+        <v>127207662</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1278,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615850</v>
+        <v>616073</v>
       </c>
       <c r="R8" t="n">
-        <v>7312339</v>
+        <v>7312575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127207662</v>
+        <v>127216040</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,39 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616073</v>
+        <v>615850</v>
       </c>
       <c r="R9" t="n">
-        <v>7312575</v>
+        <v>7312339</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127213092</v>
+        <v>127202904</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,34 +1773,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615949</v>
+        <v>615830</v>
       </c>
       <c r="R13" t="n">
-        <v>7312406</v>
+        <v>7312490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1833,6 +1838,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i gammal levande gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127202904</v>
+        <v>127213092</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,39 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615830</v>
+        <v>615949</v>
       </c>
       <c r="R14" t="n">
-        <v>7312490</v>
+        <v>7312406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1935,11 +1940,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i gammal levande gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127215584</v>
+        <v>127201066</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,34 +2961,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615886</v>
+        <v>615797</v>
       </c>
       <c r="R25" t="n">
-        <v>7312367</v>
+        <v>7312466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,6 +3026,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3047,7 +3057,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127217294</v>
+        <v>127215584</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3082,10 +3092,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615776</v>
+        <v>615886</v>
       </c>
       <c r="R26" t="n">
-        <v>7312289</v>
+        <v>7312367</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3144,10 +3154,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127201066</v>
+        <v>127217294</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3155,39 +3165,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615797</v>
+        <v>615776</v>
       </c>
       <c r="R27" t="n">
-        <v>7312466</v>
+        <v>7312289</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3220,11 +3225,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127211062</v>
+        <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>91344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616059</v>
+        <v>615794</v>
       </c>
       <c r="R2" t="n">
-        <v>7312517</v>
+        <v>7312501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127201655</v>
+        <v>127199651</v>
       </c>
       <c r="B3" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615794</v>
+        <v>615757</v>
       </c>
       <c r="R3" t="n">
-        <v>7312501</v>
+        <v>7312430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127199651</v>
+        <v>127211062</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615757</v>
+        <v>616059</v>
       </c>
       <c r="R4" t="n">
-        <v>7312430</v>
+        <v>7312517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127202530</v>
+        <v>127215400</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,34 +1977,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615835</v>
+        <v>615915</v>
       </c>
       <c r="R15" t="n">
-        <v>7312494</v>
+        <v>7312380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,48 +2088,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R16" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127199651</v>
+        <v>127211062</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615757</v>
+        <v>616059</v>
       </c>
       <c r="R3" t="n">
-        <v>7312430</v>
+        <v>7312517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127211062</v>
+        <v>127199651</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616059</v>
+        <v>615757</v>
       </c>
       <c r="R4" t="n">
-        <v>7312517</v>
+        <v>7312430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127207662</v>
+        <v>127206480</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79097</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,39 +1278,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616073</v>
+        <v>616032</v>
       </c>
       <c r="R8" t="n">
-        <v>7312575</v>
+        <v>7312582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127216040</v>
+        <v>127207662</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1375,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615850</v>
+        <v>616073</v>
       </c>
       <c r="R9" t="n">
-        <v>7312339</v>
+        <v>7312575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1440,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127206480</v>
+        <v>127216040</v>
       </c>
       <c r="B10" t="n">
-        <v>79093</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,34 +1482,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616032</v>
+        <v>615850</v>
       </c>
       <c r="R10" t="n">
-        <v>7312582</v>
+        <v>7312339</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,7 +1571,7 @@
         <v>127202357</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127209866</v>
       </c>
       <c r="B12" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127202904</v>
+        <v>127213092</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,39 +1773,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615830</v>
+        <v>615949</v>
       </c>
       <c r="R13" t="n">
-        <v>7312490</v>
+        <v>7312406</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,11 +1833,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i gammal levande gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127213092</v>
+        <v>127202904</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1870,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615949</v>
+        <v>615830</v>
       </c>
       <c r="R14" t="n">
-        <v>7312406</v>
+        <v>7312490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,6 +1935,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i gammal levande gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,7 +1969,7 @@
         <v>127215400</v>
       </c>
       <c r="B15" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>127202530</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>127199175</v>
       </c>
       <c r="B17" t="n">
-        <v>79093</v>
+        <v>79097</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127215841</v>
+        <v>127210564</v>
       </c>
       <c r="B18" t="n">
-        <v>79093</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2282,21 +2282,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615874</v>
+        <v>616097</v>
       </c>
       <c r="R18" t="n">
-        <v>7312344</v>
+        <v>7312522</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127210564</v>
+        <v>127215841</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79097</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616097</v>
+        <v>615874</v>
       </c>
       <c r="R19" t="n">
-        <v>7312522</v>
+        <v>7312344</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
         <v>127200148</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127205089</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>127208158</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>127198843</v>
       </c>
       <c r="B24" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127201066</v>
+        <v>127217294</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,39 +2961,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615797</v>
+        <v>615776</v>
       </c>
       <c r="R25" t="n">
-        <v>7312466</v>
+        <v>7312289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3026,11 +3021,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3060,7 +3050,7 @@
         <v>127215584</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3154,10 +3144,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127217294</v>
+        <v>127201066</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3165,34 +3155,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615776</v>
+        <v>615797</v>
       </c>
       <c r="R27" t="n">
-        <v>7312289</v>
+        <v>7312466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,6 +3220,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>127209165</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>127216622</v>
       </c>
       <c r="B30" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>127202125</v>
       </c>
       <c r="B31" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127206480</v>
+        <v>127216040</v>
       </c>
       <c r="B8" t="n">
-        <v>79097</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1278,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616032</v>
+        <v>615850</v>
       </c>
       <c r="R8" t="n">
-        <v>7312582</v>
+        <v>7312339</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127207662</v>
+        <v>127206480</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>79097</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,39 +1375,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616073</v>
+        <v>616032</v>
       </c>
       <c r="R9" t="n">
-        <v>7312575</v>
+        <v>7312582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127216040</v>
+        <v>127207662</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,34 +1472,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615850</v>
+        <v>616073</v>
       </c>
       <c r="R10" t="n">
-        <v>7312339</v>
+        <v>7312575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1537,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B15" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,48 +1977,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R15" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127202530</v>
+        <v>127215400</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,34 +2074,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615835</v>
+        <v>615915</v>
       </c>
       <c r="R16" t="n">
-        <v>7312494</v>
+        <v>7312380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127210564</v>
+        <v>127215841</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79097</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2282,21 +2282,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616097</v>
+        <v>615874</v>
       </c>
       <c r="R18" t="n">
-        <v>7312522</v>
+        <v>7312344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127215841</v>
+        <v>127210564</v>
       </c>
       <c r="B19" t="n">
-        <v>79097</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615874</v>
+        <v>616097</v>
       </c>
       <c r="R19" t="n">
-        <v>7312344</v>
+        <v>7312522</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127217294</v>
+        <v>127201066</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,34 +2961,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615776</v>
+        <v>615797</v>
       </c>
       <c r="R25" t="n">
-        <v>7312289</v>
+        <v>7312466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,6 +3026,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3144,10 +3154,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127201066</v>
+        <v>127217294</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3155,39 +3165,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615797</v>
+        <v>615776</v>
       </c>
       <c r="R27" t="n">
-        <v>7312466</v>
+        <v>7312289</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3220,11 +3225,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3348,50 +3348,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127209165</v>
+        <v>127216622</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>91591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616119</v>
+        <v>615822</v>
       </c>
       <c r="R29" t="n">
-        <v>7312620</v>
+        <v>7312329</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,11 +3419,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3455,45 +3445,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127216622</v>
+        <v>127202125</v>
       </c>
       <c r="B30" t="n">
-        <v>91591</v>
+        <v>75142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615822</v>
+        <v>615815</v>
       </c>
       <c r="R30" t="n">
-        <v>7312329</v>
+        <v>7312514</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,10 +3542,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127202125</v>
+        <v>127209165</v>
       </c>
       <c r="B31" t="n">
-        <v>75142</v>
+        <v>57661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3563,34 +3553,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615815</v>
+        <v>616119</v>
       </c>
       <c r="R31" t="n">
-        <v>7312514</v>
+        <v>7312620</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3623,6 +3618,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127201655</v>
+        <v>127211062</v>
       </c>
       <c r="B2" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615794</v>
+        <v>616059</v>
       </c>
       <c r="R2" t="n">
-        <v>7312501</v>
+        <v>7312517</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127211062</v>
+        <v>127201655</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616059</v>
+        <v>615794</v>
       </c>
       <c r="R3" t="n">
-        <v>7312517</v>
+        <v>7312501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127201066</v>
+        <v>127215584</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,39 +2961,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615797</v>
+        <v>615886</v>
       </c>
       <c r="R25" t="n">
-        <v>7312466</v>
+        <v>7312367</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3026,11 +3021,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3057,7 +3047,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127215584</v>
+        <v>127217294</v>
       </c>
       <c r="B26" t="n">
         <v>79018</v>
@@ -3092,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615886</v>
+        <v>615776</v>
       </c>
       <c r="R26" t="n">
-        <v>7312367</v>
+        <v>7312289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3154,10 +3144,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127217294</v>
+        <v>127201066</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3165,34 +3155,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615776</v>
+        <v>615797</v>
       </c>
       <c r="R27" t="n">
-        <v>7312289</v>
+        <v>7312466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,6 +3220,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127211062</v>
+        <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616059</v>
+        <v>615794</v>
       </c>
       <c r="R2" t="n">
-        <v>7312517</v>
+        <v>7312501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127201655</v>
+        <v>127211062</v>
       </c>
       <c r="B3" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615794</v>
+        <v>616059</v>
       </c>
       <c r="R3" t="n">
-        <v>7312501</v>
+        <v>7312517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127215584</v>
+        <v>127201066</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,34 +2961,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615886</v>
+        <v>615797</v>
       </c>
       <c r="R25" t="n">
-        <v>7312367</v>
+        <v>7312466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,6 +3026,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3047,7 +3057,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127217294</v>
+        <v>127215584</v>
       </c>
       <c r="B26" t="n">
         <v>79018</v>
@@ -3082,10 +3092,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615776</v>
+        <v>615886</v>
       </c>
       <c r="R26" t="n">
-        <v>7312289</v>
+        <v>7312367</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3144,10 +3154,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127201066</v>
+        <v>127217294</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3155,39 +3165,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615797</v>
+        <v>615776</v>
       </c>
       <c r="R27" t="n">
-        <v>7312466</v>
+        <v>7312289</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3220,11 +3225,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127201655</v>
+        <v>127211062</v>
       </c>
       <c r="B2" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615794</v>
+        <v>616059</v>
       </c>
       <c r="R2" t="n">
-        <v>7312501</v>
+        <v>7312517</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127211062</v>
+        <v>127201655</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616059</v>
+        <v>615794</v>
       </c>
       <c r="R3" t="n">
-        <v>7312517</v>
+        <v>7312501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127216040</v>
+        <v>127206480</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79097</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1278,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615850</v>
+        <v>616032</v>
       </c>
       <c r="R8" t="n">
-        <v>7312339</v>
+        <v>7312582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127206480</v>
+        <v>127207662</v>
       </c>
       <c r="B9" t="n">
-        <v>79097</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,34 +1375,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616032</v>
+        <v>616073</v>
       </c>
       <c r="R9" t="n">
-        <v>7312582</v>
+        <v>7312575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1440,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127207662</v>
+        <v>127216040</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,39 +1482,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616073</v>
+        <v>615850</v>
       </c>
       <c r="R10" t="n">
-        <v>7312575</v>
+        <v>7312339</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127202530</v>
+        <v>127215400</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,34 +1977,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615835</v>
+        <v>615915</v>
       </c>
       <c r="R15" t="n">
-        <v>7312494</v>
+        <v>7312380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B16" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,48 +2088,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R16" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127215841</v>
+        <v>127210564</v>
       </c>
       <c r="B18" t="n">
-        <v>79097</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2282,21 +2282,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615874</v>
+        <v>616097</v>
       </c>
       <c r="R18" t="n">
-        <v>7312344</v>
+        <v>7312522</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127210564</v>
+        <v>127215841</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79097</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616097</v>
+        <v>615874</v>
       </c>
       <c r="R19" t="n">
-        <v>7312522</v>
+        <v>7312344</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127203005</v>
+        <v>127208158</v>
       </c>
       <c r="B22" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,34 +2670,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Innervik, Innervik, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615847</v>
+        <v>616118</v>
       </c>
       <c r="R22" t="n">
-        <v>7312503</v>
+        <v>7312594</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127208158</v>
+        <v>127203005</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,34 +2767,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Innervik, Innervik, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616118</v>
+        <v>615847</v>
       </c>
       <c r="R23" t="n">
-        <v>7312594</v>
+        <v>7312503</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127201066</v>
+        <v>127217294</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,39 +2961,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615797</v>
+        <v>615776</v>
       </c>
       <c r="R25" t="n">
-        <v>7312466</v>
+        <v>7312289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3026,11 +3021,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3154,10 +3144,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127217294</v>
+        <v>127201066</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3165,34 +3155,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615776</v>
+        <v>615797</v>
       </c>
       <c r="R27" t="n">
-        <v>7312289</v>
+        <v>7312466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,6 +3220,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3348,45 +3348,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127216622</v>
+        <v>127209165</v>
       </c>
       <c r="B29" t="n">
-        <v>91591</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615822</v>
+        <v>616119</v>
       </c>
       <c r="R29" t="n">
-        <v>7312329</v>
+        <v>7312620</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,6 +3424,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3542,50 +3552,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127209165</v>
+        <v>127216622</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>91591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>616119</v>
+        <v>615822</v>
       </c>
       <c r="R31" t="n">
-        <v>7312620</v>
+        <v>7312329</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3618,11 +3623,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127211062</v>
+        <v>127199651</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616059</v>
+        <v>615757</v>
       </c>
       <c r="R2" t="n">
-        <v>7312517</v>
+        <v>7312430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127201655</v>
+        <v>127211062</v>
       </c>
       <c r="B3" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615794</v>
+        <v>616059</v>
       </c>
       <c r="R3" t="n">
-        <v>7312501</v>
+        <v>7312517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127199651</v>
+        <v>127201655</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615757</v>
+        <v>615794</v>
       </c>
       <c r="R4" t="n">
-        <v>7312430</v>
+        <v>7312501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -3348,50 +3348,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127209165</v>
+        <v>127216622</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>91591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616119</v>
+        <v>615822</v>
       </c>
       <c r="R29" t="n">
-        <v>7312620</v>
+        <v>7312329</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,11 +3419,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3455,10 +3445,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127202125</v>
+        <v>127209165</v>
       </c>
       <c r="B30" t="n">
-        <v>75142</v>
+        <v>57661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3466,34 +3456,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615815</v>
+        <v>616119</v>
       </c>
       <c r="R30" t="n">
-        <v>7312514</v>
+        <v>7312620</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3526,6 +3521,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3552,45 +3552,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127216622</v>
+        <v>127202125</v>
       </c>
       <c r="B31" t="n">
-        <v>91591</v>
+        <v>75142</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615822</v>
+        <v>615815</v>
       </c>
       <c r="R31" t="n">
-        <v>7312329</v>
+        <v>7312514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127199651</v>
+        <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615757</v>
+        <v>615794</v>
       </c>
       <c r="R2" t="n">
-        <v>7312430</v>
+        <v>7312501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127211062</v>
+        <v>127199651</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616059</v>
+        <v>615757</v>
       </c>
       <c r="R3" t="n">
-        <v>7312517</v>
+        <v>7312430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127201655</v>
+        <v>127211062</v>
       </c>
       <c r="B4" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615794</v>
+        <v>616059</v>
       </c>
       <c r="R4" t="n">
-        <v>7312501</v>
+        <v>7312517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127206480</v>
+        <v>127216040</v>
       </c>
       <c r="B8" t="n">
-        <v>79097</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1278,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616032</v>
+        <v>615850</v>
       </c>
       <c r="R8" t="n">
-        <v>7312582</v>
+        <v>7312339</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127207662</v>
+        <v>127206480</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>79099</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,39 +1375,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616073</v>
+        <v>616032</v>
       </c>
       <c r="R9" t="n">
-        <v>7312575</v>
+        <v>7312582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127216040</v>
+        <v>127207662</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,34 +1472,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615850</v>
+        <v>616073</v>
       </c>
       <c r="R10" t="n">
-        <v>7312339</v>
+        <v>7312575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1537,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,7 +1571,7 @@
         <v>127202357</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127209866</v>
       </c>
       <c r="B12" t="n">
-        <v>91344</v>
+        <v>91346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127213092</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>127202904</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B15" t="n">
-        <v>57821</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,48 +1977,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R15" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127202530</v>
+        <v>127215400</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,34 +2074,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615835</v>
+        <v>615915</v>
       </c>
       <c r="R16" t="n">
-        <v>7312494</v>
+        <v>7312380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2177,7 +2177,7 @@
         <v>127199175</v>
       </c>
       <c r="B17" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>127210564</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>127215841</v>
       </c>
       <c r="B19" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>127200148</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127205089</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127208158</v>
+        <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,34 +2670,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Innervik, Innervik, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616118</v>
+        <v>615847</v>
       </c>
       <c r="R22" t="n">
-        <v>7312594</v>
+        <v>7312503</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127203005</v>
+        <v>127208158</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,34 +2767,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Innervik, Innervik, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615847</v>
+        <v>616118</v>
       </c>
       <c r="R23" t="n">
-        <v>7312503</v>
+        <v>7312594</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
         <v>127198843</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127217294</v>
+        <v>127201066</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,34 +2961,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615776</v>
+        <v>615797</v>
       </c>
       <c r="R25" t="n">
-        <v>7312289</v>
+        <v>7312466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,6 +3026,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3047,10 +3057,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127215584</v>
+        <v>127217294</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3082,10 +3092,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615886</v>
+        <v>615776</v>
       </c>
       <c r="R26" t="n">
-        <v>7312367</v>
+        <v>7312289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3144,10 +3154,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127201066</v>
+        <v>127215584</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3155,39 +3165,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615797</v>
+        <v>615886</v>
       </c>
       <c r="R27" t="n">
-        <v>7312466</v>
+        <v>7312367</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3220,11 +3225,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3348,45 +3348,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127216622</v>
+        <v>127202125</v>
       </c>
       <c r="B29" t="n">
-        <v>91591</v>
+        <v>75144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615822</v>
+        <v>615815</v>
       </c>
       <c r="R29" t="n">
-        <v>7312329</v>
+        <v>7312514</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3445,50 +3445,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127209165</v>
+        <v>127216622</v>
       </c>
       <c r="B30" t="n">
-        <v>57661</v>
+        <v>91593</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>616119</v>
+        <v>615822</v>
       </c>
       <c r="R30" t="n">
-        <v>7312620</v>
+        <v>7312329</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3521,11 +3516,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3552,10 +3542,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127202125</v>
+        <v>127209165</v>
       </c>
       <c r="B31" t="n">
-        <v>75142</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3563,34 +3553,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615815</v>
+        <v>616119</v>
       </c>
       <c r="R31" t="n">
-        <v>7312514</v>
+        <v>7312620</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3623,6 +3618,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127199651</v>
+        <v>127211062</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615757</v>
+        <v>616059</v>
       </c>
       <c r="R3" t="n">
-        <v>7312430</v>
+        <v>7312517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127211062</v>
+        <v>127199651</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616059</v>
+        <v>615757</v>
       </c>
       <c r="R4" t="n">
-        <v>7312517</v>
+        <v>7312430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127206480</v>
+        <v>127207662</v>
       </c>
       <c r="B9" t="n">
-        <v>79099</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,34 +1375,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616032</v>
+        <v>616073</v>
       </c>
       <c r="R9" t="n">
-        <v>7312582</v>
+        <v>7312575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1440,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127207662</v>
+        <v>127206480</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>79099</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,39 +1482,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616073</v>
+        <v>616032</v>
       </c>
       <c r="R10" t="n">
-        <v>7312575</v>
+        <v>7312582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127210564</v>
+        <v>127215841</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79099</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2282,21 +2282,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616097</v>
+        <v>615874</v>
       </c>
       <c r="R18" t="n">
-        <v>7312522</v>
+        <v>7312344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127215841</v>
+        <v>127210564</v>
       </c>
       <c r="B19" t="n">
-        <v>79099</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615874</v>
+        <v>616097</v>
       </c>
       <c r="R19" t="n">
-        <v>7312344</v>
+        <v>7312522</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127201066</v>
+        <v>127215584</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,39 +2961,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615797</v>
+        <v>615886</v>
       </c>
       <c r="R25" t="n">
-        <v>7312466</v>
+        <v>7312367</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3026,11 +3021,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3154,10 +3144,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127215584</v>
+        <v>127201066</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3165,34 +3155,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615886</v>
+        <v>615797</v>
       </c>
       <c r="R27" t="n">
-        <v>7312367</v>
+        <v>7312466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,6 +3220,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3348,10 +3348,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127202125</v>
+        <v>127209165</v>
       </c>
       <c r="B29" t="n">
-        <v>75144</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3359,34 +3359,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615815</v>
+        <v>616119</v>
       </c>
       <c r="R29" t="n">
-        <v>7312514</v>
+        <v>7312620</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,6 +3424,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3542,10 +3552,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127209165</v>
+        <v>127202125</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>75144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3553,39 +3563,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>616119</v>
+        <v>615815</v>
       </c>
       <c r="R31" t="n">
-        <v>7312620</v>
+        <v>7312514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3618,11 +3623,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127209866</v>
       </c>
       <c r="B12" t="n">
-        <v>91346</v>
+        <v>91352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127202530</v>
+        <v>127215400</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,34 +1977,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615835</v>
+        <v>615915</v>
       </c>
       <c r="R15" t="n">
-        <v>7312494</v>
+        <v>7312380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,48 +2088,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R16" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2662,7 +2662,7 @@
         <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>127216622</v>
       </c>
       <c r="B30" t="n">
-        <v>91593</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127211062</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127199651</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127216040</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127207662</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127206480</v>
       </c>
       <c r="B10" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127202357</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127209866</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127213092</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>127202904</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,48 +1977,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R15" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127202530</v>
+        <v>127215400</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,34 +2074,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615835</v>
+        <v>615915</v>
       </c>
       <c r="R16" t="n">
-        <v>7312494</v>
+        <v>7312380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2177,7 +2177,7 @@
         <v>127199175</v>
       </c>
       <c r="B17" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>127215841</v>
       </c>
       <c r="B18" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>127210564</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>127200148</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127205089</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>127208158</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>127198843</v>
       </c>
       <c r="B24" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>127215584</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>127217294</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127201066</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>127209165</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>127216622</v>
       </c>
       <c r="B30" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>127202125</v>
       </c>
       <c r="B31" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127211062</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127199651</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127216040</v>
+        <v>127206480</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1278,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615850</v>
+        <v>616032</v>
       </c>
       <c r="R8" t="n">
-        <v>7312339</v>
+        <v>7312582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127207662</v>
+        <v>127216040</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,39 +1375,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616073</v>
+        <v>615850</v>
       </c>
       <c r="R9" t="n">
-        <v>7312575</v>
+        <v>7312339</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127206480</v>
+        <v>127207662</v>
       </c>
       <c r="B10" t="n">
-        <v>79102</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,34 +1472,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616032</v>
+        <v>616073</v>
       </c>
       <c r="R10" t="n">
-        <v>7312582</v>
+        <v>7312575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1537,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127202357</v>
+        <v>127209866</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>91363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615826</v>
+        <v>616160</v>
       </c>
       <c r="R11" t="n">
-        <v>7312510</v>
+        <v>7312538</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127209866</v>
+        <v>127202357</v>
       </c>
       <c r="B12" t="n">
-        <v>91355</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,34 +1676,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616160</v>
+        <v>615826</v>
       </c>
       <c r="R12" t="n">
-        <v>7312538</v>
+        <v>7312510</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,7 +1765,7 @@
         <v>127213092</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>127202904</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>127202530</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>127215400</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>127199175</v>
       </c>
       <c r="B17" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>127215841</v>
       </c>
       <c r="B18" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>127210564</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>127200148</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127205089</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>127208158</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>127198843</v>
       </c>
       <c r="B24" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>127215584</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>127217294</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127201066</v>
       </c>
       <c r="B27" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>127209165</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3455,45 +3455,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127216622</v>
+        <v>127202125</v>
       </c>
       <c r="B30" t="n">
-        <v>91602</v>
+        <v>75153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615822</v>
+        <v>615815</v>
       </c>
       <c r="R30" t="n">
-        <v>7312329</v>
+        <v>7312514</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,45 +3552,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127202125</v>
+        <v>127216622</v>
       </c>
       <c r="B31" t="n">
-        <v>75147</v>
+        <v>91610</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>65</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615815</v>
+        <v>615822</v>
       </c>
       <c r="R31" t="n">
-        <v>7312514</v>
+        <v>7312329</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127201655</v>
+        <v>127199651</v>
       </c>
       <c r="B2" t="n">
-        <v>91367</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615794</v>
+        <v>615757</v>
       </c>
       <c r="R2" t="n">
-        <v>7312501</v>
+        <v>7312430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127211062</v>
+        <v>127201655</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616059</v>
+        <v>615794</v>
       </c>
       <c r="R3" t="n">
-        <v>7312517</v>
+        <v>7312501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127199651</v>
+        <v>127211062</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615757</v>
+        <v>616059</v>
       </c>
       <c r="R4" t="n">
-        <v>7312430</v>
+        <v>7312517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127206480</v>
+        <v>127216040</v>
       </c>
       <c r="B8" t="n">
-        <v>79108</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1278,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616032</v>
+        <v>615850</v>
       </c>
       <c r="R8" t="n">
-        <v>7312582</v>
+        <v>7312339</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127216040</v>
+        <v>127207662</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,34 +1375,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615850</v>
+        <v>616073</v>
       </c>
       <c r="R9" t="n">
-        <v>7312339</v>
+        <v>7312575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1440,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127207662</v>
+        <v>127206480</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>79108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,39 +1482,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616073</v>
+        <v>616032</v>
       </c>
       <c r="R10" t="n">
-        <v>7312575</v>
+        <v>7312582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127209866</v>
+        <v>127202357</v>
       </c>
       <c r="B11" t="n">
-        <v>91363</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616160</v>
+        <v>615826</v>
       </c>
       <c r="R11" t="n">
-        <v>7312538</v>
+        <v>7312510</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127202357</v>
+        <v>127209866</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>91364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,34 +1676,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615826</v>
+        <v>616160</v>
       </c>
       <c r="R12" t="n">
-        <v>7312510</v>
+        <v>7312538</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2662,7 +2662,7 @@
         <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3455,45 +3455,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127202125</v>
+        <v>127216622</v>
       </c>
       <c r="B30" t="n">
-        <v>75153</v>
+        <v>91611</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>65</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615815</v>
+        <v>615822</v>
       </c>
       <c r="R30" t="n">
-        <v>7312514</v>
+        <v>7312329</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,45 +3552,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127216622</v>
+        <v>127202125</v>
       </c>
       <c r="B31" t="n">
-        <v>91610</v>
+        <v>75153</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615822</v>
+        <v>615815</v>
       </c>
       <c r="R31" t="n">
-        <v>7312329</v>
+        <v>7312514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127199651</v>
+        <v>127201655</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>91337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615757</v>
+        <v>615794</v>
       </c>
       <c r="R2" t="n">
-        <v>7312430</v>
+        <v>7312501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127201655</v>
+        <v>127211062</v>
       </c>
       <c r="B3" t="n">
-        <v>91368</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615794</v>
+        <v>616059</v>
       </c>
       <c r="R3" t="n">
-        <v>7312501</v>
+        <v>7312517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127211062</v>
+        <v>127199651</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616059</v>
+        <v>615757</v>
       </c>
       <c r="R4" t="n">
-        <v>7312517</v>
+        <v>7312430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91368</v>
+        <v>91337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91646</v>
+        <v>91615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91368</v>
+        <v>91337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127216040</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127207662</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127206480</v>
       </c>
       <c r="B10" t="n">
-        <v>79108</v>
+        <v>79090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127202357</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127209866</v>
       </c>
       <c r="B12" t="n">
-        <v>91364</v>
+        <v>91333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127213092</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>127202904</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127202530</v>
+        <v>127215400</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>57817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,34 +1977,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615835</v>
+        <v>615915</v>
       </c>
       <c r="R15" t="n">
-        <v>7312494</v>
+        <v>7312380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B16" t="n">
-        <v>57832</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,48 +2088,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R16" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2177,7 +2177,7 @@
         <v>127199175</v>
       </c>
       <c r="B17" t="n">
-        <v>79108</v>
+        <v>79090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>127215841</v>
       </c>
       <c r="B18" t="n">
-        <v>79108</v>
+        <v>79090</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>127210564</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>127200148</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127205089</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>91368</v>
+        <v>91337</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>127208158</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>127198843</v>
       </c>
       <c r="B24" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>127215584</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>127217294</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127201066</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91368</v>
+        <v>91337</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>127209165</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>127216622</v>
       </c>
       <c r="B30" t="n">
-        <v>91611</v>
+        <v>91580</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>127202125</v>
       </c>
       <c r="B31" t="n">
-        <v>75153</v>
+        <v>75135</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127201655</v>
+        <v>127199651</v>
       </c>
       <c r="B2" t="n">
-        <v>91337</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615794</v>
+        <v>615757</v>
       </c>
       <c r="R2" t="n">
-        <v>7312501</v>
+        <v>7312430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127211062</v>
+        <v>127201655</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>91368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616059</v>
+        <v>615794</v>
       </c>
       <c r="R3" t="n">
-        <v>7312517</v>
+        <v>7312501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127199651</v>
+        <v>127211062</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615757</v>
+        <v>616059</v>
       </c>
       <c r="R4" t="n">
-        <v>7312430</v>
+        <v>7312517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>127201525</v>
       </c>
       <c r="B5" t="n">
-        <v>91337</v>
+        <v>91368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127205990</v>
       </c>
       <c r="B6" t="n">
-        <v>91615</v>
+        <v>91646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127216772</v>
       </c>
       <c r="B7" t="n">
-        <v>91337</v>
+        <v>91368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127216040</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127207662</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127206480</v>
       </c>
       <c r="B10" t="n">
-        <v>79090</v>
+        <v>79108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>127202357</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127209866</v>
       </c>
       <c r="B12" t="n">
-        <v>91333</v>
+        <v>91364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127213092</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>127202904</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B15" t="n">
-        <v>57817</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,48 +1977,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R15" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127202530</v>
+        <v>127215400</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>57832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,34 +2074,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615835</v>
+        <v>615915</v>
       </c>
       <c r="R16" t="n">
-        <v>7312494</v>
+        <v>7312380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2177,7 +2177,7 @@
         <v>127199175</v>
       </c>
       <c r="B17" t="n">
-        <v>79090</v>
+        <v>79108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>127215841</v>
       </c>
       <c r="B18" t="n">
-        <v>79090</v>
+        <v>79108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>127210564</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>127200148</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>127205089</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>127203005</v>
       </c>
       <c r="B22" t="n">
-        <v>91337</v>
+        <v>91368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>127208158</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>127198843</v>
       </c>
       <c r="B24" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>127215584</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>127217294</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127201066</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>127197440</v>
       </c>
       <c r="B28" t="n">
-        <v>91337</v>
+        <v>91368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>127209165</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>127216622</v>
       </c>
       <c r="B30" t="n">
-        <v>91580</v>
+        <v>91611</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>127202125</v>
       </c>
       <c r="B31" t="n">
-        <v>75135</v>
+        <v>75153</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127199651</v>
+        <v>127216622</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615757</v>
+        <v>615822</v>
       </c>
       <c r="R2" t="n">
-        <v>7312430</v>
+        <v>7312329</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127201655</v>
+        <v>127199175</v>
       </c>
       <c r="B3" t="n">
-        <v>91368</v>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615794</v>
+        <v>615741</v>
       </c>
       <c r="R3" t="n">
-        <v>7312501</v>
+        <v>7312426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127211062</v>
+        <v>127215841</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616059</v>
+        <v>615874</v>
       </c>
       <c r="R4" t="n">
-        <v>7312517</v>
+        <v>7312344</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack i tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127201525</v>
+        <v>127200148</v>
       </c>
       <c r="B5" t="n">
-        <v>91368</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615789</v>
+        <v>615766</v>
       </c>
       <c r="R5" t="n">
-        <v>7312497</v>
+        <v>7312426</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,45 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127205990</v>
+        <v>127213092</v>
       </c>
       <c r="B6" t="n">
-        <v>91646</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616016</v>
+        <v>615949</v>
       </c>
       <c r="R6" t="n">
-        <v>7312593</v>
+        <v>7312406</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127216772</v>
+        <v>127215584</v>
       </c>
       <c r="B7" t="n">
-        <v>91368</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615802</v>
+        <v>615886</v>
       </c>
       <c r="R7" t="n">
-        <v>7312328</v>
+        <v>7312367</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1260,11 @@
         <v>127216040</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1364,50 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127207662</v>
+        <v>127217294</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Rakkåive, Rakkåive, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616073</v>
+        <v>615776</v>
       </c>
       <c r="R9" t="n">
-        <v>7312575</v>
+        <v>7312289</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,11 +1425,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127206480</v>
+        <v>127215400</v>
       </c>
       <c r="B10" t="n">
-        <v>79108</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,34 +1462,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616032</v>
+        <v>615915</v>
       </c>
       <c r="R10" t="n">
-        <v>7312582</v>
+        <v>7312380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127202357</v>
+        <v>127205990</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615826</v>
+        <v>616016</v>
       </c>
       <c r="R11" t="n">
-        <v>7312510</v>
+        <v>7312593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127209866</v>
+        <v>127206480</v>
       </c>
       <c r="B12" t="n">
-        <v>91364</v>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,34 +1670,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616160</v>
+        <v>616032</v>
       </c>
       <c r="R12" t="n">
-        <v>7312538</v>
+        <v>7312582</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,32 +1756,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127213092</v>
+        <v>127209866</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1791,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615949</v>
+        <v>616160</v>
       </c>
       <c r="R13" t="n">
-        <v>7312406</v>
+        <v>7312538</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1859,50 +1853,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127202904</v>
+        <v>127199651</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615830</v>
+        <v>615757</v>
       </c>
       <c r="R14" t="n">
-        <v>7312490</v>
+        <v>7312430</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1935,11 +1924,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i gammal levande gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,14 +1950,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127202530</v>
+        <v>127202357</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2001,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615835</v>
+        <v>615826</v>
       </c>
       <c r="R15" t="n">
-        <v>7312494</v>
+        <v>7312510</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,59 +2047,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127215400</v>
+        <v>127202530</v>
       </c>
       <c r="B16" t="n">
-        <v>57832</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
+          <t>Sapedberget, Sapedberget, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615915</v>
+        <v>615835</v>
       </c>
       <c r="R16" t="n">
-        <v>7312380</v>
+        <v>7312494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,32 +2144,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127199175</v>
+        <v>127205089</v>
       </c>
       <c r="B17" t="n">
-        <v>79108</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2209,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615741</v>
+        <v>615940</v>
       </c>
       <c r="R17" t="n">
-        <v>7312426</v>
+        <v>7312503</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,45 +2241,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127215841</v>
+        <v>127208158</v>
       </c>
       <c r="B18" t="n">
-        <v>79108</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Innervik, Innervik, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615874</v>
+        <v>616118</v>
       </c>
       <c r="R18" t="n">
-        <v>7312344</v>
+        <v>7312594</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2371,11 +2341,11 @@
         <v>127210564</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2465,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127200148</v>
+        <v>127202125</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,21 +2446,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2500,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615766</v>
+        <v>615815</v>
       </c>
       <c r="R20" t="n">
-        <v>7312426</v>
+        <v>7312514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127205089</v>
+        <v>127198843</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,21 +2543,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2597,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615940</v>
+        <v>615725</v>
       </c>
       <c r="R21" t="n">
-        <v>7312503</v>
+        <v>7312446</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127203005</v>
+        <v>127201066</v>
       </c>
       <c r="B22" t="n">
-        <v>91368</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,34 +2640,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615847</v>
+        <v>615797</v>
       </c>
       <c r="R22" t="n">
-        <v>7312503</v>
+        <v>7312466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2730,6 +2705,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på en färsk granlåga.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2756,10 +2736,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127208158</v>
+        <v>127202904</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,34 +2747,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Innervik, Innervik, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616118</v>
+        <v>615830</v>
       </c>
       <c r="R23" t="n">
-        <v>7312594</v>
+        <v>7312490</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2827,6 +2812,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i gammal levande gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2853,10 +2843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127198843</v>
+        <v>127207662</v>
       </c>
       <c r="B24" t="n">
-        <v>79647</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2864,34 +2854,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615725</v>
+        <v>616073</v>
       </c>
       <c r="R24" t="n">
-        <v>7312446</v>
+        <v>7312575</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2924,6 +2919,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127215584</v>
+        <v>127209165</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,34 +2961,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615886</v>
+        <v>616119</v>
       </c>
       <c r="R25" t="n">
-        <v>7312367</v>
+        <v>7312620</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,6 +3026,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3047,10 +3057,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127217294</v>
+        <v>127211062</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3058,34 +3068,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
+          <t>Maskaures utl., Maskaures utl., Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615776</v>
+        <v>616059</v>
       </c>
       <c r="R26" t="n">
-        <v>7312289</v>
+        <v>7312517</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,6 +3135,11 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3141,511 +3161,6 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>127201066</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57672</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>615797</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7312466</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på en färsk granlåga.</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>127197440</v>
-      </c>
-      <c r="B28" t="n">
-        <v>91368</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>615736</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7312375</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>127209165</v>
-      </c>
-      <c r="B29" t="n">
-        <v>57672</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Maskaures utl., Maskaures utl., Pi lm</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>616119</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7312620</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran.</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>127216622</v>
-      </c>
-      <c r="B30" t="n">
-        <v>91611</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>65</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Fläckporing</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Anthoporia albobrunnea</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Rakkåive, Rakkåive, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>615822</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7312329</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>127202125</v>
-      </c>
-      <c r="B31" t="n">
-        <v>75153</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Sapedberget, Sapedberget, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>615815</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7312514</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31143-2025 artfynd.xlsx
+++ b/artfynd/A 31143-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127216622</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127205990</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127199175</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127206480</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127215841</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127209866</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127199651</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127200148</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127202357</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127202530</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127205089</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127208158</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127210564</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127213092</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127215584</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127216040</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127217294</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127202125</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127198843</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127201066</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127202904</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2836,6 +2946,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127207662</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2943,6 +3058,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127209165</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3050,6 +3170,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127211062</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3161,8 +3286,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127215400</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>